--- a/data/leaf_temperatures.xlsx
+++ b/data/leaf_temperatures.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/heating/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5452990-E01B-744F-BA8C-88E7DC879261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10DC7345-AA72-C246-988E-30A98E654015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-35940" yWindow="760" windowWidth="28800" windowHeight="15800" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
   </bookViews>
@@ -12498,6 +12498,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008F3A2D606D2A7F41B72D5682D1CD7008" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d76c20a2b3afad6e4ced79b91df906ab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48b2884d-86bd-41bc-b5ea-f3a63e495149" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7e8f2e6da924d638fc8dc52abe2ab2bf" ns2:_="">
     <xsd:import namespace="48b2884d-86bd-41bc-b5ea-f3a63e495149"/>
@@ -12629,22 +12644,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7DAC2BA-C817-4ECF-8DFA-94F5C2AE87D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12660,21 +12677,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/leaf_temperatures.xlsx
+++ b/data/leaf_temperatures.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/heating/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10DC7345-AA72-C246-988E-30A98E654015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7F5A7E-B768-2D4D-BBBF-DDCCC4FA5B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35940" yWindow="760" windowWidth="28800" windowHeight="15800" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
+    <workbookView xWindow="-38100" yWindow="260" windowWidth="36160" windowHeight="20460" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
   </bookViews>
   <sheets>
     <sheet name="temperatures" sheetId="5" r:id="rId1"/>
     <sheet name="Read Me" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">temperatures!$A$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">temperatures!$A$1:$H$497</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -564,7 +564,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="2">
-        <v>34.799999999999997</v>
+        <v>31.1</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2">
-        <v>33.9</v>
+        <v>31.4</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -615,7 +615,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2">
-        <v>33.799999999999997</v>
+        <v>31.5</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -641,7 +641,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="2">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -693,7 +693,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -720,7 +720,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="2">
-        <v>31.5</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -747,7 +747,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>31.4</v>
+        <v>33.9</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -774,7 +774,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="2">
-        <v>31.1</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -801,7 +801,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="2">
-        <v>35.700000000000003</v>
+        <v>32.5</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -827,7 +827,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="2">
-        <v>35.200000000000003</v>
+        <v>32.5</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -853,7 +853,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="2">
-        <v>34.6</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -879,7 +879,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="2">
-        <v>33.799999999999997</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -931,7 +931,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="2">
-        <v>33</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -957,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="2">
-        <v>33</v>
+        <v>34.6</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -983,7 +983,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="2">
-        <v>32.5</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1009,7 +1009,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="2">
-        <v>32.5</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1035,7 +1035,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="4">
-        <v>34.5</v>
+        <v>32.1</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1060,7 +1060,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="4">
-        <v>34.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1085,7 +1085,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="4">
-        <v>34.299999999999997</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -1110,7 +1110,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="4">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1160,7 +1160,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="4">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1185,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="4">
-        <v>32.200000000000003</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="4">
-        <v>32.200000000000003</v>
+        <v>34.4</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="4">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -1260,7 +1260,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="2">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -1285,7 +1285,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="2">
-        <v>32.5</v>
+        <v>31.7</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -1310,7 +1310,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="2">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="2">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -1385,7 +1385,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="2">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -1410,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="2">
-        <v>31.8</v>
+        <v>32.4</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -1435,7 +1435,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="2">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="2">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -1485,7 +1485,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="4">
-        <v>34.6</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -1510,7 +1510,7 @@
         <v>2</v>
       </c>
       <c r="G39" s="4">
-        <v>34.5</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -1535,7 +1535,7 @@
         <v>2</v>
       </c>
       <c r="G40" s="4">
-        <v>34.4</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -1560,7 +1560,7 @@
         <v>2</v>
       </c>
       <c r="G41" s="4">
-        <v>33.799999999999997</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -1610,7 +1610,7 @@
         <v>2</v>
       </c>
       <c r="G43" s="4">
-        <v>33.299999999999997</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -1635,7 +1635,7 @@
         <v>2</v>
       </c>
       <c r="G44" s="4">
-        <v>32.299999999999997</v>
+        <v>34.4</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -1660,7 +1660,7 @@
         <v>2</v>
       </c>
       <c r="G45" s="4">
-        <v>32.299999999999997</v>
+        <v>34.5</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -1685,7 +1685,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="4">
-        <v>32.299999999999997</v>
+        <v>34.6</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -1710,7 +1710,7 @@
         <v>2</v>
       </c>
       <c r="G47" s="2">
-        <v>44.4</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -1735,7 +1735,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="2">
-        <v>43.9</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -1760,7 +1760,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="2">
-        <v>43.2</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -1785,7 +1785,7 @@
         <v>2</v>
       </c>
       <c r="G50" s="2">
-        <v>42.3</v>
+        <v>40.4</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -1835,7 +1835,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="2">
-        <v>40.4</v>
+        <v>42.3</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -1860,7 +1860,7 @@
         <v>2</v>
       </c>
       <c r="G53" s="2">
-        <v>36.299999999999997</v>
+        <v>43.2</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -1885,7 +1885,7 @@
         <v>2</v>
       </c>
       <c r="G54" s="2">
-        <v>35.299999999999997</v>
+        <v>43.9</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -1910,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="G55" s="2">
-        <v>35.200000000000003</v>
+        <v>44.4</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -1935,7 +1935,7 @@
         <v>2</v>
       </c>
       <c r="G56" s="4">
-        <v>38.1</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -1960,7 +1960,7 @@
         <v>2</v>
       </c>
       <c r="G57" s="4">
-        <v>36.799999999999997</v>
+        <v>33.6</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -1985,7 +1985,7 @@
         <v>2</v>
       </c>
       <c r="G58" s="4">
-        <v>36.4</v>
+        <v>33.9</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -2010,7 +2010,7 @@
         <v>2</v>
       </c>
       <c r="G59" s="4">
-        <v>36.1</v>
+        <v>34.6</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -2060,7 +2060,7 @@
         <v>2</v>
       </c>
       <c r="G61" s="4">
-        <v>34.6</v>
+        <v>36.1</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -2085,7 +2085,7 @@
         <v>2</v>
       </c>
       <c r="G62" s="4">
-        <v>33.9</v>
+        <v>36.4</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -2110,7 +2110,7 @@
         <v>2</v>
       </c>
       <c r="G63" s="4">
-        <v>33.6</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -2135,7 +2135,7 @@
         <v>2</v>
       </c>
       <c r="G64" s="4">
-        <v>32.299999999999997</v>
+        <v>38.1</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -2160,7 +2160,7 @@
         <v>2</v>
       </c>
       <c r="G65" s="2">
-        <v>40.200000000000003</v>
+        <v>32.9</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -2185,7 +2185,7 @@
         <v>2</v>
       </c>
       <c r="G66" s="2">
-        <v>38</v>
+        <v>32.9</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -2210,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="G67" s="2">
-        <v>36.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -2235,7 +2235,7 @@
         <v>2</v>
       </c>
       <c r="G68" s="2">
-        <v>34.799999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -2285,7 +2285,7 @@
         <v>2</v>
       </c>
       <c r="G70" s="2">
-        <v>33.9</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -2310,7 +2310,7 @@
         <v>2</v>
       </c>
       <c r="G71" s="2">
-        <v>33</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -2335,7 +2335,7 @@
         <v>2</v>
       </c>
       <c r="G72" s="2">
-        <v>32.9</v>
+        <v>38</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -2360,7 +2360,7 @@
         <v>2</v>
       </c>
       <c r="G73" s="2">
-        <v>32.9</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -2385,7 +2385,7 @@
         <v>2</v>
       </c>
       <c r="G74" s="2">
-        <v>37</v>
+        <v>31.2</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -2410,7 +2410,7 @@
         <v>2</v>
       </c>
       <c r="G75" s="2">
-        <v>36.200000000000003</v>
+        <v>31.3</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -2435,7 +2435,7 @@
         <v>2</v>
       </c>
       <c r="G76" s="2">
-        <v>36.1</v>
+        <v>31.5</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -2460,7 +2460,7 @@
         <v>2</v>
       </c>
       <c r="G77" s="2">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -2510,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="G79" s="2">
-        <v>32</v>
+        <v>32.6</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -2535,7 +2535,7 @@
         <v>2</v>
       </c>
       <c r="G80" s="2">
-        <v>31.5</v>
+        <v>36.1</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -2560,7 +2560,7 @@
         <v>2</v>
       </c>
       <c r="G81" s="2">
-        <v>31.3</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -2585,7 +2585,7 @@
         <v>2</v>
       </c>
       <c r="G82" s="2">
-        <v>31.2</v>
+        <v>37</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -2610,7 +2610,7 @@
         <v>2</v>
       </c>
       <c r="G83" s="2">
-        <v>38.5</v>
+        <v>31.8</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -2635,7 +2635,7 @@
         <v>2</v>
       </c>
       <c r="G84" s="2">
-        <v>35.5</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -2660,7 +2660,7 @@
         <v>2</v>
       </c>
       <c r="G85" s="2">
-        <v>33.299999999999997</v>
+        <v>32.4</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -2685,7 +2685,7 @@
         <v>2</v>
       </c>
       <c r="G86" s="2">
-        <v>33.299999999999997</v>
+        <v>33</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -2735,7 +2735,7 @@
         <v>2</v>
       </c>
       <c r="G88" s="2">
-        <v>33</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
@@ -2760,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="G89" s="2">
-        <v>32.4</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
@@ -2785,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="G90" s="2">
-        <v>32.200000000000003</v>
+        <v>35.5</v>
       </c>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
@@ -2810,7 +2810,7 @@
         <v>2</v>
       </c>
       <c r="G91" s="2">
-        <v>31.8</v>
+        <v>38.5</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
@@ -2835,7 +2835,7 @@
         <v>2</v>
       </c>
       <c r="G92" s="2">
-        <v>45.9</v>
+        <v>32.6</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
@@ -2860,7 +2860,7 @@
         <v>2</v>
       </c>
       <c r="G93" s="2">
-        <v>44.8</v>
+        <v>32.9</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
@@ -2885,7 +2885,7 @@
         <v>2</v>
       </c>
       <c r="G94" s="2">
-        <v>44.7</v>
+        <v>34.1</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
@@ -2910,7 +2910,7 @@
         <v>2</v>
       </c>
       <c r="G95" s="2">
-        <v>44.2</v>
+        <v>39.1</v>
       </c>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
@@ -2960,7 +2960,7 @@
         <v>2</v>
       </c>
       <c r="G97" s="2">
-        <v>39.1</v>
+        <v>44.2</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
@@ -2985,7 +2985,7 @@
         <v>2</v>
       </c>
       <c r="G98" s="2">
-        <v>34.1</v>
+        <v>44.7</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
@@ -3010,7 +3010,7 @@
         <v>2</v>
       </c>
       <c r="G99" s="2">
-        <v>32.9</v>
+        <v>44.8</v>
       </c>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
@@ -3035,7 +3035,7 @@
         <v>2</v>
       </c>
       <c r="G100" s="2">
-        <v>32.6</v>
+        <v>45.9</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
@@ -3060,7 +3060,7 @@
         <v>4</v>
       </c>
       <c r="G101" s="2">
-        <v>31.2</v>
+        <v>29.8</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
@@ -3085,7 +3085,7 @@
         <v>4</v>
       </c>
       <c r="G102" s="2">
-        <v>30.6</v>
+        <v>29.9</v>
       </c>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
@@ -3110,7 +3110,7 @@
         <v>4</v>
       </c>
       <c r="G103" s="2">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
@@ -3135,7 +3135,7 @@
         <v>4</v>
       </c>
       <c r="G104" s="2">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
@@ -3185,7 +3185,7 @@
         <v>4</v>
       </c>
       <c r="G106" s="2">
-        <v>30.1</v>
+        <v>30.4</v>
       </c>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
@@ -3210,7 +3210,7 @@
         <v>4</v>
       </c>
       <c r="G107" s="2">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
@@ -3235,7 +3235,7 @@
         <v>4</v>
       </c>
       <c r="G108" s="2">
-        <v>29.9</v>
+        <v>30.6</v>
       </c>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
@@ -3260,7 +3260,7 @@
         <v>4</v>
       </c>
       <c r="G109" s="2">
-        <v>29.8</v>
+        <v>31.2</v>
       </c>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
@@ -3285,7 +3285,7 @@
         <v>4</v>
       </c>
       <c r="G110" s="2">
-        <v>33.299999999999997</v>
+        <v>29.6</v>
       </c>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
@@ -3310,7 +3310,7 @@
         <v>4</v>
       </c>
       <c r="G111" s="2">
-        <v>33.299999999999997</v>
+        <v>30.4</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
@@ -3335,7 +3335,7 @@
         <v>4</v>
       </c>
       <c r="G112" s="2">
-        <v>31.3</v>
+        <v>30.5</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
@@ -3360,7 +3360,7 @@
         <v>4</v>
       </c>
       <c r="G113" s="2">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
@@ -3410,7 +3410,7 @@
         <v>4</v>
       </c>
       <c r="G115" s="2">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
@@ -3435,7 +3435,7 @@
         <v>4</v>
       </c>
       <c r="G116" s="2">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
@@ -3460,7 +3460,7 @@
         <v>4</v>
       </c>
       <c r="G117" s="2">
-        <v>30.4</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
@@ -3485,7 +3485,7 @@
         <v>4</v>
       </c>
       <c r="G118" s="2">
-        <v>29.6</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
@@ -3510,7 +3510,7 @@
         <v>4</v>
       </c>
       <c r="G119" s="2">
-        <v>35.1</v>
+        <v>34</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
@@ -3535,7 +3535,7 @@
         <v>4</v>
       </c>
       <c r="G120" s="2">
-        <v>34.799999999999997</v>
+        <v>34</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
@@ -3560,7 +3560,7 @@
         <v>4</v>
       </c>
       <c r="G121" s="2">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
@@ -3585,7 +3585,7 @@
         <v>4</v>
       </c>
       <c r="G122" s="2">
-        <v>34.229999999999997</v>
+        <v>34.1</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
@@ -3635,7 +3635,7 @@
         <v>4</v>
       </c>
       <c r="G124" s="2">
-        <v>34.1</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
@@ -3660,7 +3660,7 @@
         <v>4</v>
       </c>
       <c r="G125" s="2">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
@@ -3685,7 +3685,7 @@
         <v>4</v>
       </c>
       <c r="G126" s="2">
-        <v>34</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
@@ -3710,7 +3710,7 @@
         <v>4</v>
       </c>
       <c r="G127" s="2">
-        <v>34</v>
+        <v>35.1</v>
       </c>
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
@@ -3735,7 +3735,7 @@
         <v>4</v>
       </c>
       <c r="G128" s="4">
-        <v>33</v>
+        <v>30.4</v>
       </c>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
@@ -3760,7 +3760,7 @@
         <v>4</v>
       </c>
       <c r="G129" s="4">
-        <v>32.4</v>
+        <v>30.8</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
@@ -3785,7 +3785,7 @@
         <v>4</v>
       </c>
       <c r="G130" s="4">
-        <v>31.6</v>
+        <v>30.9</v>
       </c>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
@@ -3810,7 +3810,7 @@
         <v>4</v>
       </c>
       <c r="G131" s="4">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
@@ -3860,7 +3860,7 @@
         <v>4</v>
       </c>
       <c r="G133" s="4">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
@@ -3885,7 +3885,7 @@
         <v>4</v>
       </c>
       <c r="G134" s="4">
-        <v>30.9</v>
+        <v>31.6</v>
       </c>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
@@ -3910,7 +3910,7 @@
         <v>4</v>
       </c>
       <c r="G135" s="4">
-        <v>30.8</v>
+        <v>32.4</v>
       </c>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
@@ -3935,7 +3935,7 @@
         <v>4</v>
       </c>
       <c r="G136" s="4">
-        <v>30.4</v>
+        <v>33</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
@@ -3960,7 +3960,7 @@
         <v>4</v>
       </c>
       <c r="G137" s="2">
-        <v>34.700000000000003</v>
+        <v>31.6</v>
       </c>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
@@ -3985,7 +3985,7 @@
         <v>4</v>
       </c>
       <c r="G138" s="2">
-        <v>32.4</v>
+        <v>31.6</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
@@ -4010,7 +4010,7 @@
         <v>4</v>
       </c>
       <c r="G139" s="2">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
@@ -4035,7 +4035,7 @@
         <v>4</v>
       </c>
       <c r="G140" s="2">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
@@ -4085,7 +4085,7 @@
         <v>4</v>
       </c>
       <c r="G142" s="2">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
@@ -4110,7 +4110,7 @@
         <v>4</v>
       </c>
       <c r="G143" s="2">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
@@ -4135,7 +4135,7 @@
         <v>4</v>
       </c>
       <c r="G144" s="2">
-        <v>31.6</v>
+        <v>32.4</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
@@ -4160,7 +4160,7 @@
         <v>4</v>
       </c>
       <c r="G145" s="2">
-        <v>31.6</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
@@ -4185,7 +4185,7 @@
         <v>4</v>
       </c>
       <c r="G146" s="2">
-        <v>43.3</v>
+        <v>30.6</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
@@ -4210,7 +4210,7 @@
         <v>4</v>
       </c>
       <c r="G147" s="2">
-        <v>35.5</v>
+        <v>30.8</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
@@ -4235,7 +4235,7 @@
         <v>4</v>
       </c>
       <c r="G148" s="2">
-        <v>34.1</v>
+        <v>30.9</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
@@ -4260,7 +4260,7 @@
         <v>4</v>
       </c>
       <c r="G149" s="2">
-        <v>31.7</v>
+        <v>31</v>
       </c>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
@@ -4310,7 +4310,7 @@
         <v>4</v>
       </c>
       <c r="G151" s="2">
-        <v>31</v>
+        <v>31.7</v>
       </c>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
@@ -4335,7 +4335,7 @@
         <v>4</v>
       </c>
       <c r="G152" s="2">
-        <v>30.9</v>
+        <v>34.1</v>
       </c>
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
@@ -4360,7 +4360,7 @@
         <v>4</v>
       </c>
       <c r="G153" s="2">
-        <v>30.8</v>
+        <v>35.5</v>
       </c>
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
@@ -4385,7 +4385,7 @@
         <v>4</v>
       </c>
       <c r="G154" s="2">
-        <v>30.6</v>
+        <v>43.3</v>
       </c>
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
@@ -4410,7 +4410,7 @@
         <v>4</v>
       </c>
       <c r="G155" s="2">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
@@ -4435,7 +4435,7 @@
         <v>4</v>
       </c>
       <c r="G156" s="2">
-        <v>33.299999999999997</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
@@ -4460,7 +4460,7 @@
         <v>4</v>
       </c>
       <c r="G157" s="2">
-        <v>33.299999999999997</v>
+        <v>32.5</v>
       </c>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
@@ -4485,7 +4485,7 @@
         <v>4</v>
       </c>
       <c r="G158" s="2">
-        <v>33.1</v>
+        <v>32.5</v>
       </c>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
@@ -4535,7 +4535,7 @@
         <v>4</v>
       </c>
       <c r="G160" s="2">
-        <v>32.5</v>
+        <v>33.1</v>
       </c>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
@@ -4560,7 +4560,7 @@
         <v>4</v>
       </c>
       <c r="G161" s="2">
-        <v>32.5</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
@@ -4585,7 +4585,7 @@
         <v>4</v>
       </c>
       <c r="G162" s="2">
-        <v>32.200000000000003</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
@@ -4610,7 +4610,7 @@
         <v>4</v>
       </c>
       <c r="G163" s="2">
-        <v>31.5</v>
+        <v>33.5</v>
       </c>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
@@ -4635,7 +4635,7 @@
         <v>4</v>
       </c>
       <c r="G164" s="4">
-        <v>33.799999999999997</v>
+        <v>31.3</v>
       </c>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
@@ -4660,7 +4660,7 @@
         <v>4</v>
       </c>
       <c r="G165" s="4">
-        <v>33.5</v>
+        <v>31.4</v>
       </c>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
@@ -4685,7 +4685,7 @@
         <v>4</v>
       </c>
       <c r="G166" s="4">
-        <v>32.799999999999997</v>
+        <v>31.7</v>
       </c>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
@@ -4710,7 +4710,7 @@
         <v>4</v>
       </c>
       <c r="G167" s="4">
-        <v>32.299999999999997</v>
+        <v>31.9</v>
       </c>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
@@ -4760,7 +4760,7 @@
         <v>4</v>
       </c>
       <c r="G169" s="4">
-        <v>31.9</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
@@ -4785,7 +4785,7 @@
         <v>4</v>
       </c>
       <c r="G170" s="4">
-        <v>31.7</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
@@ -4810,7 +4810,7 @@
         <v>4</v>
       </c>
       <c r="G171" s="4">
-        <v>31.4</v>
+        <v>33.5</v>
       </c>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
@@ -4835,7 +4835,7 @@
         <v>4</v>
       </c>
       <c r="G172" s="4">
-        <v>31.3</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
@@ -4860,7 +4860,7 @@
         <v>4</v>
       </c>
       <c r="G173" s="4">
-        <v>33.700000000000003</v>
+        <v>31.4</v>
       </c>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
@@ -4885,7 +4885,7 @@
         <v>4</v>
       </c>
       <c r="G174" s="4">
-        <v>31.9</v>
+        <v>31.4</v>
       </c>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
@@ -4910,7 +4910,7 @@
         <v>4</v>
       </c>
       <c r="G175" s="4">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
@@ -5010,7 +5010,7 @@
         <v>4</v>
       </c>
       <c r="G179" s="4">
-        <v>31.5</v>
+        <v>31.8</v>
       </c>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
@@ -5035,7 +5035,7 @@
         <v>4</v>
       </c>
       <c r="G180" s="4">
-        <v>31.4</v>
+        <v>31.9</v>
       </c>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
@@ -5060,7 +5060,7 @@
         <v>4</v>
       </c>
       <c r="G181" s="4">
-        <v>31.4</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
@@ -5085,7 +5085,7 @@
         <v>4</v>
       </c>
       <c r="G182" s="2">
-        <v>35.299999999999997</v>
+        <v>31.1</v>
       </c>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
@@ -5110,7 +5110,7 @@
         <v>4</v>
       </c>
       <c r="G183" s="2">
-        <v>34.5</v>
+        <v>31.2</v>
       </c>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
@@ -5135,7 +5135,7 @@
         <v>4</v>
       </c>
       <c r="G184" s="2">
-        <v>33.9</v>
+        <v>31.3</v>
       </c>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
@@ -5160,7 +5160,7 @@
         <v>4</v>
       </c>
       <c r="G185" s="2">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
@@ -5210,7 +5210,7 @@
         <v>4</v>
       </c>
       <c r="G187" s="2">
-        <v>31.9</v>
+        <v>32.5</v>
       </c>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
@@ -5235,7 +5235,7 @@
         <v>4</v>
       </c>
       <c r="G188" s="2">
-        <v>31.3</v>
+        <v>33.9</v>
       </c>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
@@ -5260,7 +5260,7 @@
         <v>4</v>
       </c>
       <c r="G189" s="2">
-        <v>31.2</v>
+        <v>34.5</v>
       </c>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
@@ -5285,7 +5285,7 @@
         <v>4</v>
       </c>
       <c r="G190" s="2">
-        <v>31.1</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
@@ -5310,7 +5310,7 @@
         <v>4</v>
       </c>
       <c r="G191" s="2">
-        <v>33.9</v>
+        <v>31.2</v>
       </c>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
@@ -5335,7 +5335,7 @@
         <v>4</v>
       </c>
       <c r="G192" s="2">
-        <v>32.5</v>
+        <v>31.3</v>
       </c>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
@@ -5360,7 +5360,7 @@
         <v>4</v>
       </c>
       <c r="G193" s="2">
-        <v>32.299999999999997</v>
+        <v>31.4</v>
       </c>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
@@ -5385,7 +5385,7 @@
         <v>4</v>
       </c>
       <c r="G194" s="2">
-        <v>32</v>
+        <v>31.5</v>
       </c>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
@@ -5435,7 +5435,7 @@
         <v>4</v>
       </c>
       <c r="G196" s="2">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
@@ -5460,7 +5460,7 @@
         <v>4</v>
       </c>
       <c r="G197" s="2">
-        <v>31.4</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
@@ -5485,7 +5485,7 @@
         <v>4</v>
       </c>
       <c r="G198" s="2">
-        <v>31.3</v>
+        <v>32.5</v>
       </c>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
@@ -5510,7 +5510,7 @@
         <v>4</v>
       </c>
       <c r="G199" s="2">
-        <v>31.2</v>
+        <v>33.9</v>
       </c>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
@@ -5535,7 +5535,7 @@
         <v>5</v>
       </c>
       <c r="G200" s="2">
-        <v>38.799999999999997</v>
+        <v>33.6</v>
       </c>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
@@ -5560,7 +5560,7 @@
         <v>5</v>
       </c>
       <c r="G201" s="2">
-        <v>38.299999999999997</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
@@ -5585,7 +5585,7 @@
         <v>5</v>
       </c>
       <c r="G202" s="2">
-        <v>37.799999999999997</v>
+        <v>35</v>
       </c>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
@@ -5610,7 +5610,7 @@
         <v>5</v>
       </c>
       <c r="G203" s="2">
-        <v>37.6</v>
+        <v>36</v>
       </c>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
@@ -5660,7 +5660,7 @@
         <v>5</v>
       </c>
       <c r="G205" s="2">
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
@@ -5685,7 +5685,7 @@
         <v>5</v>
       </c>
       <c r="G206" s="2">
-        <v>35</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
@@ -5710,7 +5710,7 @@
         <v>5</v>
       </c>
       <c r="G207" s="2">
-        <v>34.200000000000003</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
@@ -5735,7 +5735,7 @@
         <v>5</v>
       </c>
       <c r="G208" s="2">
-        <v>33.6</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
@@ -5760,7 +5760,7 @@
         <v>5</v>
       </c>
       <c r="G209" s="2">
-        <v>38.9</v>
+        <v>33</v>
       </c>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
@@ -5785,7 +5785,7 @@
         <v>5</v>
       </c>
       <c r="G210" s="2">
-        <v>38.5</v>
+        <v>33.1</v>
       </c>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
@@ -5810,7 +5810,7 @@
         <v>5</v>
       </c>
       <c r="G211" s="2">
-        <v>38.299999999999997</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
@@ -5835,7 +5835,7 @@
         <v>5</v>
       </c>
       <c r="G212" s="2">
-        <v>37.200000000000003</v>
+        <v>35</v>
       </c>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
@@ -5885,7 +5885,7 @@
         <v>5</v>
       </c>
       <c r="G214" s="2">
-        <v>35</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
@@ -5910,7 +5910,7 @@
         <v>5</v>
       </c>
       <c r="G215" s="2">
-        <v>33.200000000000003</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
@@ -5935,7 +5935,7 @@
         <v>5</v>
       </c>
       <c r="G216" s="2">
-        <v>33.1</v>
+        <v>38.5</v>
       </c>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
@@ -5960,7 +5960,7 @@
         <v>5</v>
       </c>
       <c r="G217" s="2">
-        <v>33</v>
+        <v>38.9</v>
       </c>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
@@ -5985,7 +5985,7 @@
         <v>5</v>
       </c>
       <c r="G218" s="2">
-        <v>45.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
@@ -6010,7 +6010,7 @@
         <v>5</v>
       </c>
       <c r="G219" s="2">
-        <v>44.5</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
@@ -6035,7 +6035,7 @@
         <v>5</v>
       </c>
       <c r="G220" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
@@ -6060,7 +6060,7 @@
         <v>5</v>
       </c>
       <c r="G221" s="2">
-        <v>42.6</v>
+        <v>42.1</v>
       </c>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
@@ -6110,7 +6110,7 @@
         <v>5</v>
       </c>
       <c r="G223" s="2">
-        <v>42.1</v>
+        <v>42.6</v>
       </c>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
@@ -6135,7 +6135,7 @@
         <v>5</v>
       </c>
       <c r="G224" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
@@ -6160,7 +6160,7 @@
         <v>5</v>
       </c>
       <c r="G225" s="2">
-        <v>40.799999999999997</v>
+        <v>44.5</v>
       </c>
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
@@ -6185,7 +6185,7 @@
         <v>5</v>
       </c>
       <c r="G226" s="2">
-        <v>40.299999999999997</v>
+        <v>45.3</v>
       </c>
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
@@ -6210,9 +6210,8 @@
         <v>5</v>
       </c>
       <c r="G227" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="H227" s="2"/>
+        <v>34.799999999999997</v>
+      </c>
       <c r="I227" s="2"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
@@ -6235,9 +6234,8 @@
         <v>5</v>
       </c>
       <c r="G228" s="4">
-        <v>37.1</v>
-      </c>
-      <c r="H228" s="2"/>
+        <v>35</v>
+      </c>
       <c r="I228" s="2"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
@@ -6260,7 +6258,7 @@
         <v>5</v>
       </c>
       <c r="G229" s="4">
-        <v>37</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
@@ -6285,7 +6283,7 @@
         <v>5</v>
       </c>
       <c r="G230" s="4">
-        <v>36.200000000000003</v>
+        <v>35.6</v>
       </c>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
@@ -6335,7 +6333,7 @@
         <v>5</v>
       </c>
       <c r="G232" s="4">
-        <v>35.6</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
@@ -6360,7 +6358,7 @@
         <v>5</v>
       </c>
       <c r="G233" s="4">
-        <v>35.299999999999997</v>
+        <v>37</v>
       </c>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
@@ -6385,8 +6383,9 @@
         <v>5</v>
       </c>
       <c r="G234" s="4">
-        <v>35</v>
-      </c>
+        <v>37.1</v>
+      </c>
+      <c r="H234" s="2"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="5" t="s">
@@ -6408,8 +6407,9 @@
         <v>5</v>
       </c>
       <c r="G235" s="4">
-        <v>34.799999999999997</v>
-      </c>
+        <v>37.6</v>
+      </c>
+      <c r="H235" s="2"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="5" t="s">
@@ -6431,7 +6431,7 @@
         <v>5</v>
       </c>
       <c r="G236" s="4">
-        <v>36.5</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
@@ -6454,7 +6454,7 @@
         <v>5</v>
       </c>
       <c r="G237" s="4">
-        <v>36.1</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
@@ -6477,7 +6477,7 @@
         <v>5</v>
       </c>
       <c r="G238" s="4">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
@@ -6500,7 +6500,7 @@
         <v>5</v>
       </c>
       <c r="G239" s="4">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
@@ -6546,7 +6546,7 @@
         <v>5</v>
       </c>
       <c r="G241" s="4">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -6569,7 +6569,7 @@
         <v>5</v>
       </c>
       <c r="G242" s="4">
-        <v>33.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
@@ -6592,7 +6592,7 @@
         <v>5</v>
       </c>
       <c r="G243" s="4">
-        <v>31.6</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
@@ -6615,7 +6615,7 @@
         <v>5</v>
       </c>
       <c r="G244" s="4">
-        <v>31.6</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
@@ -6638,7 +6638,7 @@
         <v>5</v>
       </c>
       <c r="G245" s="2">
-        <v>44.5</v>
+        <v>35.700000000000003</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
@@ -6661,7 +6661,7 @@
         <v>5</v>
       </c>
       <c r="G246" s="2">
-        <v>43.3</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
@@ -6684,7 +6684,7 @@
         <v>5</v>
       </c>
       <c r="G247" s="2">
-        <v>42.5</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.2">
@@ -6707,7 +6707,7 @@
         <v>5</v>
       </c>
       <c r="G248" s="2">
-        <v>38.4</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
@@ -6753,7 +6753,7 @@
         <v>5</v>
       </c>
       <c r="G250" s="2">
-        <v>37.9</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -6776,7 +6776,7 @@
         <v>5</v>
       </c>
       <c r="G251" s="2">
-        <v>37.4</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
@@ -6799,7 +6799,7 @@
         <v>5</v>
       </c>
       <c r="G252" s="2">
-        <v>37.299999999999997</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -6822,7 +6822,7 @@
         <v>5</v>
       </c>
       <c r="G253" s="2">
-        <v>35.700000000000003</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -6845,7 +6845,7 @@
         <v>5</v>
       </c>
       <c r="G254" s="2">
-        <v>40.6</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
@@ -6868,7 +6868,7 @@
         <v>5</v>
       </c>
       <c r="G255" s="2">
-        <v>40.200000000000003</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.2">
@@ -6891,7 +6891,7 @@
         <v>5</v>
       </c>
       <c r="G256" s="2">
-        <v>39.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
@@ -6983,7 +6983,7 @@
         <v>5</v>
       </c>
       <c r="G260" s="2">
-        <v>37.9</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
@@ -7006,7 +7006,7 @@
         <v>5</v>
       </c>
       <c r="G261" s="2">
-        <v>37.4</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
@@ -7029,7 +7029,7 @@
         <v>5</v>
       </c>
       <c r="G262" s="2">
-        <v>36.4</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
@@ -7052,7 +7052,7 @@
         <v>5</v>
       </c>
       <c r="G263" s="4">
-        <v>39</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
@@ -7075,7 +7075,7 @@
         <v>5</v>
       </c>
       <c r="G264" s="4">
-        <v>38.9</v>
+        <v>34.700000000000003</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
@@ -7098,7 +7098,7 @@
         <v>5</v>
       </c>
       <c r="G265" s="4">
-        <v>36.4</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
@@ -7121,7 +7121,7 @@
         <v>5</v>
       </c>
       <c r="G266" s="4">
-        <v>35.299999999999997</v>
+        <v>35</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
@@ -7167,7 +7167,7 @@
         <v>5</v>
       </c>
       <c r="G268" s="4">
-        <v>35</v>
+        <v>35.299999999999997</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
@@ -7190,7 +7190,7 @@
         <v>5</v>
       </c>
       <c r="G269" s="4">
-        <v>34.799999999999997</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
@@ -7213,7 +7213,7 @@
         <v>5</v>
       </c>
       <c r="G270" s="4">
-        <v>34.700000000000003</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
@@ -7236,7 +7236,7 @@
         <v>5</v>
       </c>
       <c r="G271" s="4">
-        <v>33.799999999999997</v>
+        <v>39</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
@@ -7259,7 +7259,7 @@
         <v>5</v>
       </c>
       <c r="G272" s="2">
-        <v>45.7</v>
+        <v>33.200000000000003</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.2">
@@ -7282,7 +7282,7 @@
         <v>5</v>
       </c>
       <c r="G273" s="2">
-        <v>38.799999999999997</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.2">
@@ -7305,7 +7305,7 @@
         <v>5</v>
       </c>
       <c r="G274" s="2">
-        <v>38.200000000000003</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.2">
@@ -7328,7 +7328,7 @@
         <v>5</v>
       </c>
       <c r="G275" s="2">
-        <v>37.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.2">
@@ -7374,7 +7374,7 @@
         <v>5</v>
       </c>
       <c r="G277" s="2">
-        <v>36.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.2">
@@ -7397,7 +7397,7 @@
         <v>5</v>
       </c>
       <c r="G278" s="2">
-        <v>33.6</v>
+        <v>38.200000000000003</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.2">
@@ -7420,7 +7420,7 @@
         <v>5</v>
       </c>
       <c r="G279" s="2">
-        <v>33.299999999999997</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.2">
@@ -7443,7 +7443,7 @@
         <v>5</v>
       </c>
       <c r="G280" s="2">
-        <v>33.200000000000003</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.2">
@@ -7466,7 +7466,7 @@
         <v>5</v>
       </c>
       <c r="G281" s="4">
-        <v>41.9</v>
+        <v>35.799999999999997</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.2">
@@ -7489,7 +7489,7 @@
         <v>5</v>
       </c>
       <c r="G282" s="4">
-        <v>40.4</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.2">
@@ -7512,7 +7512,7 @@
         <v>5</v>
       </c>
       <c r="G283" s="4">
-        <v>39.700000000000003</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.2">
@@ -7535,7 +7535,7 @@
         <v>5</v>
       </c>
       <c r="G284" s="4">
-        <v>39.299999999999997</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.2">
@@ -7581,7 +7581,7 @@
         <v>5</v>
       </c>
       <c r="G286" s="4">
-        <v>38.5</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.2">
@@ -7604,7 +7604,7 @@
         <v>5</v>
       </c>
       <c r="G287" s="4">
-        <v>38.1</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
@@ -7627,7 +7627,7 @@
         <v>5</v>
       </c>
       <c r="G288" s="4">
-        <v>37.6</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.2">
@@ -7650,7 +7650,7 @@
         <v>5</v>
       </c>
       <c r="G289" s="4">
-        <v>35.799999999999997</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.2">
@@ -7673,7 +7673,7 @@
         <v>5</v>
       </c>
       <c r="G290" s="2">
-        <v>37.9</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.2">
@@ -7696,7 +7696,7 @@
         <v>5</v>
       </c>
       <c r="G291" s="2">
-        <v>37.700000000000003</v>
+        <v>29</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
@@ -7719,7 +7719,7 @@
         <v>5</v>
       </c>
       <c r="G292" s="2">
-        <v>36.6</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
@@ -7742,7 +7742,7 @@
         <v>5</v>
       </c>
       <c r="G293" s="2">
-        <v>35.299999999999997</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
@@ -7788,7 +7788,7 @@
         <v>5</v>
       </c>
       <c r="G295" s="2">
-        <v>33.4</v>
+        <v>35.299999999999997</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
@@ -7811,7 +7811,7 @@
         <v>5</v>
       </c>
       <c r="G296" s="2">
-        <v>30.7</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -7834,7 +7834,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="2">
-        <v>29</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -7857,7 +7857,7 @@
         <v>5</v>
       </c>
       <c r="G298" s="2">
-        <v>28.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
@@ -7880,7 +7880,7 @@
         <v>4</v>
       </c>
       <c r="G299" s="6">
-        <v>43.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -7903,7 +7903,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="6">
-        <v>42.4</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -7926,7 +7926,7 @@
         <v>4</v>
       </c>
       <c r="G301" s="6">
-        <v>42</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
@@ -7949,7 +7949,7 @@
         <v>4</v>
       </c>
       <c r="G302" s="6">
-        <v>40.6</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
@@ -7995,7 +7995,7 @@
         <v>4</v>
       </c>
       <c r="G304" s="6">
-        <v>39.9</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
@@ -8018,7 +8018,7 @@
         <v>4</v>
       </c>
       <c r="G305" s="6">
-        <v>38.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
@@ -8041,7 +8041,7 @@
         <v>4</v>
       </c>
       <c r="G306" s="6">
-        <v>38.9</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
@@ -8064,7 +8064,7 @@
         <v>4</v>
       </c>
       <c r="G307" s="6">
-        <v>38</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
@@ -8087,7 +8087,7 @@
         <v>4</v>
       </c>
       <c r="G308">
-        <v>38.700000000000003</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
@@ -8110,7 +8110,7 @@
         <v>4</v>
       </c>
       <c r="G309">
-        <v>38.6</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
@@ -8133,7 +8133,7 @@
         <v>4</v>
       </c>
       <c r="G310">
-        <v>38.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
@@ -8156,7 +8156,7 @@
         <v>4</v>
       </c>
       <c r="G311">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
@@ -8202,7 +8202,7 @@
         <v>4</v>
       </c>
       <c r="G313">
-        <v>38.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
@@ -8225,7 +8225,7 @@
         <v>4</v>
       </c>
       <c r="G314">
-        <v>38</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
@@ -8248,7 +8248,7 @@
         <v>4</v>
       </c>
       <c r="G315">
-        <v>37.700000000000003</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
@@ -8271,7 +8271,7 @@
         <v>4</v>
       </c>
       <c r="G316">
-        <v>37.5</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
@@ -8501,7 +8501,7 @@
         <v>4</v>
       </c>
       <c r="G326" s="6">
-        <v>40.799999999999997</v>
+        <v>38.299999999999997</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
@@ -8524,7 +8524,7 @@
         <v>4</v>
       </c>
       <c r="G327" s="6">
-        <v>40.4</v>
+        <v>38.299999999999997</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
@@ -8547,7 +8547,7 @@
         <v>4</v>
       </c>
       <c r="G328" s="6">
-        <v>39</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
@@ -8570,7 +8570,7 @@
         <v>4</v>
       </c>
       <c r="G329" s="6">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
@@ -8616,7 +8616,7 @@
         <v>4</v>
       </c>
       <c r="G331" s="6">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
@@ -8639,7 +8639,7 @@
         <v>4</v>
       </c>
       <c r="G332" s="6">
-        <v>38.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
@@ -8662,7 +8662,7 @@
         <v>4</v>
       </c>
       <c r="G333" s="6">
-        <v>38.299999999999997</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
@@ -8685,7 +8685,7 @@
         <v>4</v>
       </c>
       <c r="G334" s="6">
-        <v>38.299999999999997</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
@@ -8708,7 +8708,7 @@
         <v>4</v>
       </c>
       <c r="G335">
-        <v>38.700000000000003</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
@@ -8731,7 +8731,7 @@
         <v>4</v>
       </c>
       <c r="G336">
-        <v>38.6</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.2">
@@ -8754,7 +8754,7 @@
         <v>4</v>
       </c>
       <c r="G337">
-        <v>38.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
@@ -8777,7 +8777,7 @@
         <v>4</v>
       </c>
       <c r="G338">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
@@ -8823,7 +8823,7 @@
         <v>4</v>
       </c>
       <c r="G340">
-        <v>38.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
@@ -8846,7 +8846,7 @@
         <v>4</v>
       </c>
       <c r="G341">
-        <v>38</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
@@ -8869,7 +8869,7 @@
         <v>4</v>
       </c>
       <c r="G342">
-        <v>37.700000000000003</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
@@ -8892,7 +8892,7 @@
         <v>4</v>
       </c>
       <c r="G343">
-        <v>37.5</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.2">
@@ -8915,7 +8915,7 @@
         <v>4</v>
       </c>
       <c r="G344">
-        <v>44.8</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
@@ -8938,7 +8938,7 @@
         <v>4</v>
       </c>
       <c r="G345">
-        <v>43.1</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
@@ -8961,7 +8961,7 @@
         <v>4</v>
       </c>
       <c r="G346">
-        <v>41.3</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
@@ -8984,7 +8984,7 @@
         <v>4</v>
       </c>
       <c r="G347">
-        <v>41.1</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
@@ -9030,7 +9030,7 @@
         <v>4</v>
       </c>
       <c r="G349">
-        <v>39.9</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
@@ -9053,7 +9053,7 @@
         <v>4</v>
       </c>
       <c r="G350">
-        <v>39.5</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
@@ -9076,7 +9076,7 @@
         <v>4</v>
       </c>
       <c r="G351">
-        <v>38.700000000000003</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
@@ -9099,7 +9099,7 @@
         <v>4</v>
       </c>
       <c r="G352">
-        <v>37.4</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
@@ -9122,7 +9122,7 @@
         <v>4</v>
       </c>
       <c r="G353" s="6">
-        <v>37.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
@@ -9145,7 +9145,7 @@
         <v>4</v>
       </c>
       <c r="G354" s="6">
-        <v>37.299999999999997</v>
+        <v>36.200000000000003</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
@@ -9168,7 +9168,7 @@
         <v>4</v>
       </c>
       <c r="G355" s="6">
-        <v>37.200000000000003</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
@@ -9191,7 +9191,7 @@
         <v>4</v>
       </c>
       <c r="G356" s="6">
-        <v>37.1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
@@ -9237,7 +9237,7 @@
         <v>4</v>
       </c>
       <c r="G358" s="6">
-        <v>37</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
@@ -9260,7 +9260,7 @@
         <v>4</v>
       </c>
       <c r="G359" s="6">
-        <v>36.799999999999997</v>
+        <v>37.200000000000003</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
@@ -9283,7 +9283,7 @@
         <v>4</v>
       </c>
       <c r="G360" s="6">
-        <v>36.200000000000003</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
@@ -9306,7 +9306,7 @@
         <v>4</v>
       </c>
       <c r="G361" s="6">
-        <v>36</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
@@ -9329,7 +9329,7 @@
         <v>4</v>
       </c>
       <c r="G362">
-        <v>35.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
@@ -9352,7 +9352,7 @@
         <v>4</v>
       </c>
       <c r="G363">
-        <v>34.4</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
@@ -9375,7 +9375,7 @@
         <v>4</v>
       </c>
       <c r="G364">
-        <v>33</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
@@ -9421,7 +9421,7 @@
         <v>4</v>
       </c>
       <c r="G366">
-        <v>36.9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
@@ -9444,7 +9444,7 @@
         <v>4</v>
       </c>
       <c r="G367">
-        <v>35</v>
+        <v>35.200000000000003</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
@@ -9467,7 +9467,7 @@
         <v>4</v>
       </c>
       <c r="G368">
-        <v>35.200000000000003</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.2">
@@ -9513,7 +9513,7 @@
         <v>4</v>
       </c>
       <c r="G370">
-        <v>33.799999999999997</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.2">
@@ -9536,7 +9536,7 @@
         <v>4</v>
       </c>
       <c r="G371">
-        <v>41.1</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.2">
@@ -9559,7 +9559,7 @@
         <v>4</v>
       </c>
       <c r="G372">
-        <v>41</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
@@ -9582,7 +9582,7 @@
         <v>4</v>
       </c>
       <c r="G373">
-        <v>40.700000000000003</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.2">
@@ -9605,7 +9605,7 @@
         <v>4</v>
       </c>
       <c r="G374">
-        <v>40.200000000000003</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.2">
@@ -9651,7 +9651,7 @@
         <v>4</v>
       </c>
       <c r="G376">
-        <v>39.9</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.2">
@@ -9674,7 +9674,7 @@
         <v>4</v>
       </c>
       <c r="G377">
-        <v>39.700000000000003</v>
+        <v>40.700000000000003</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.2">
@@ -9697,7 +9697,7 @@
         <v>4</v>
       </c>
       <c r="G378">
-        <v>39.700000000000003</v>
+        <v>41</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.2">
@@ -9720,7 +9720,7 @@
         <v>4</v>
       </c>
       <c r="G379">
-        <v>39.6</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.2">
@@ -9743,7 +9743,7 @@
         <v>4</v>
       </c>
       <c r="G380">
-        <v>45.3</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.2">
@@ -9766,7 +9766,7 @@
         <v>4</v>
       </c>
       <c r="G381">
-        <v>43.3</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.2">
@@ -9789,7 +9789,7 @@
         <v>4</v>
       </c>
       <c r="G382">
-        <v>42.2</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
@@ -9812,7 +9812,7 @@
         <v>4</v>
       </c>
       <c r="G383">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.2">
@@ -9858,7 +9858,7 @@
         <v>4</v>
       </c>
       <c r="G385">
-        <v>40.5</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.2">
@@ -9881,7 +9881,7 @@
         <v>4</v>
       </c>
       <c r="G386">
-        <v>40.4</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.2">
@@ -9904,7 +9904,7 @@
         <v>4</v>
       </c>
       <c r="G387">
-        <v>40.1</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.2">
@@ -9927,7 +9927,7 @@
         <v>4</v>
       </c>
       <c r="G388">
-        <v>39.299999999999997</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.2">
@@ -9950,7 +9950,7 @@
         <v>4</v>
       </c>
       <c r="G389">
-        <v>42.1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
@@ -9973,7 +9973,7 @@
         <v>4</v>
       </c>
       <c r="G390">
-        <v>40.9</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.2">
@@ -9996,7 +9996,7 @@
         <v>4</v>
       </c>
       <c r="G391">
-        <v>40.6</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.2">
@@ -10019,7 +10019,7 @@
         <v>4</v>
       </c>
       <c r="G392">
-        <v>40.5</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
@@ -10065,7 +10065,7 @@
         <v>4</v>
       </c>
       <c r="G394">
-        <v>38.1</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
@@ -10088,7 +10088,7 @@
         <v>4</v>
       </c>
       <c r="G395">
-        <v>37.700000000000003</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
@@ -10111,7 +10111,7 @@
         <v>4</v>
       </c>
       <c r="G396">
-        <v>36.799999999999997</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
@@ -10134,7 +10134,7 @@
         <v>4</v>
       </c>
       <c r="G397">
-        <v>33</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
@@ -10157,7 +10157,7 @@
         <v>5</v>
       </c>
       <c r="G398">
-        <v>43.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
@@ -10180,7 +10180,7 @@
         <v>5</v>
       </c>
       <c r="G399">
-        <v>42.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
@@ -10203,7 +10203,7 @@
         <v>5</v>
       </c>
       <c r="G400">
-        <v>41.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
@@ -10226,7 +10226,7 @@
         <v>5</v>
       </c>
       <c r="G401">
-        <v>41.1</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
@@ -10272,7 +10272,7 @@
         <v>5</v>
       </c>
       <c r="G403">
-        <v>38.799999999999997</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
@@ -10295,7 +10295,7 @@
         <v>5</v>
       </c>
       <c r="G404">
-        <v>38.6</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
@@ -10318,7 +10318,7 @@
         <v>5</v>
       </c>
       <c r="G405">
-        <v>38.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
@@ -10341,7 +10341,7 @@
         <v>5</v>
       </c>
       <c r="G406">
-        <v>38.4</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
@@ -10364,7 +10364,7 @@
         <v>5</v>
       </c>
       <c r="G407">
-        <v>38.4</v>
+        <v>35.299999999999997</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
@@ -10387,7 +10387,7 @@
         <v>5</v>
       </c>
       <c r="G408">
-        <v>38</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
@@ -10410,7 +10410,7 @@
         <v>5</v>
       </c>
       <c r="G409">
-        <v>37.6</v>
+        <v>35.799999999999997</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
@@ -10433,7 +10433,7 @@
         <v>5</v>
       </c>
       <c r="G410">
-        <v>36.799999999999997</v>
+        <v>35.799999999999997</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
@@ -10479,7 +10479,7 @@
         <v>5</v>
       </c>
       <c r="G412">
-        <v>35.799999999999997</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
@@ -10502,7 +10502,7 @@
         <v>5</v>
       </c>
       <c r="G413">
-        <v>35.799999999999997</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
@@ -10525,7 +10525,7 @@
         <v>5</v>
       </c>
       <c r="G414">
-        <v>35.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.2">
@@ -10548,7 +10548,7 @@
         <v>5</v>
       </c>
       <c r="G415">
-        <v>35.299999999999997</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
@@ -10571,7 +10571,7 @@
         <v>5</v>
       </c>
       <c r="G416">
-        <v>41</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
@@ -10594,7 +10594,7 @@
         <v>5</v>
       </c>
       <c r="G417">
-        <v>40.799999999999997</v>
+        <v>35.200000000000003</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
@@ -10617,7 +10617,7 @@
         <v>5</v>
       </c>
       <c r="G418">
-        <v>40.4</v>
+        <v>35.299999999999997</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
@@ -10640,7 +10640,7 @@
         <v>5</v>
       </c>
       <c r="G419">
-        <v>39.9</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
@@ -10686,7 +10686,7 @@
         <v>5</v>
       </c>
       <c r="G421">
-        <v>39.299999999999997</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.2">
@@ -10709,7 +10709,7 @@
         <v>5</v>
       </c>
       <c r="G422">
-        <v>35.299999999999997</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.2">
@@ -10732,7 +10732,7 @@
         <v>5</v>
       </c>
       <c r="G423">
-        <v>35.200000000000003</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.2">
@@ -10755,7 +10755,7 @@
         <v>5</v>
       </c>
       <c r="G424">
-        <v>34.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.2">
@@ -10778,7 +10778,7 @@
         <v>5</v>
       </c>
       <c r="G425">
-        <v>38.9</v>
+        <v>36.299999999999997</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.2">
@@ -10801,7 +10801,7 @@
         <v>5</v>
       </c>
       <c r="G426">
-        <v>38.200000000000003</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.2">
@@ -10824,7 +10824,7 @@
         <v>5</v>
       </c>
       <c r="G427">
-        <v>37.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.2">
@@ -10847,7 +10847,7 @@
         <v>5</v>
       </c>
       <c r="G428">
-        <v>37.700000000000003</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.2">
@@ -10893,7 +10893,7 @@
         <v>5</v>
       </c>
       <c r="G430">
-        <v>36.700000000000003</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.2">
@@ -10916,7 +10916,7 @@
         <v>5</v>
       </c>
       <c r="G431">
-        <v>36.5</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.2">
@@ -10939,7 +10939,7 @@
         <v>5</v>
       </c>
       <c r="G432">
-        <v>36.5</v>
+        <v>38.200000000000003</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
@@ -10962,7 +10962,7 @@
         <v>5</v>
       </c>
       <c r="G433">
-        <v>36.299999999999997</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.2">
@@ -10985,7 +10985,7 @@
         <v>5</v>
       </c>
       <c r="G434">
-        <v>38.700000000000003</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.2">
@@ -11008,7 +11008,7 @@
         <v>5</v>
       </c>
       <c r="G435">
-        <v>38.299999999999997</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.2">
@@ -11031,7 +11031,7 @@
         <v>5</v>
       </c>
       <c r="G436">
-        <v>38</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.2">
@@ -11054,7 +11054,7 @@
         <v>5</v>
       </c>
       <c r="G437">
-        <v>37.9</v>
+        <v>37.799999999999997</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.2">
@@ -11100,7 +11100,7 @@
         <v>5</v>
       </c>
       <c r="G439">
-        <v>37.799999999999997</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.2">
@@ -11123,7 +11123,7 @@
         <v>5</v>
       </c>
       <c r="G440">
-        <v>37.700000000000003</v>
+        <v>38</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.2">
@@ -11146,7 +11146,7 @@
         <v>5</v>
       </c>
       <c r="G441">
-        <v>37.6</v>
+        <v>38.299999999999997</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.2">
@@ -11169,7 +11169,7 @@
         <v>5</v>
       </c>
       <c r="G442">
-        <v>37.5</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.2">
@@ -11192,7 +11192,7 @@
         <v>5</v>
       </c>
       <c r="G443">
-        <v>44.8</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.2">
@@ -11215,7 +11215,7 @@
         <v>5</v>
       </c>
       <c r="G444">
-        <v>44.4</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.2">
@@ -11238,7 +11238,7 @@
         <v>5</v>
       </c>
       <c r="G445">
-        <v>42.3</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.2">
@@ -11261,7 +11261,7 @@
         <v>5</v>
       </c>
       <c r="G446">
-        <v>41.3</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.2">
@@ -11307,7 +11307,7 @@
         <v>5</v>
       </c>
       <c r="G448">
-        <v>40.4</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.2">
@@ -11330,7 +11330,7 @@
         <v>5</v>
       </c>
       <c r="G449">
-        <v>40.299999999999997</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.2">
@@ -11353,7 +11353,7 @@
         <v>5</v>
       </c>
       <c r="G450">
-        <v>39.9</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.2">
@@ -11376,7 +11376,7 @@
         <v>5</v>
       </c>
       <c r="G451">
-        <v>39.700000000000003</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.2">
@@ -11399,7 +11399,7 @@
         <v>5</v>
       </c>
       <c r="G452">
-        <v>40.700000000000003</v>
+        <v>36.200000000000003</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.2">
@@ -11422,7 +11422,7 @@
         <v>5</v>
       </c>
       <c r="G453">
-        <v>39.1</v>
+        <v>36.200000000000003</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.2">
@@ -11445,7 +11445,7 @@
         <v>5</v>
       </c>
       <c r="G454">
-        <v>37.5</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.2">
@@ -11537,7 +11537,7 @@
         <v>5</v>
       </c>
       <c r="G458">
-        <v>37.299999999999997</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.2">
@@ -11560,7 +11560,7 @@
         <v>5</v>
       </c>
       <c r="G459">
-        <v>36.200000000000003</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.2">
@@ -11583,7 +11583,7 @@
         <v>5</v>
       </c>
       <c r="G460">
-        <v>36.200000000000003</v>
+        <v>40.700000000000003</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.2">
@@ -11606,7 +11606,7 @@
         <v>5</v>
       </c>
       <c r="G461">
-        <v>39.5</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.2">
@@ -11629,7 +11629,7 @@
         <v>5</v>
       </c>
       <c r="G462">
-        <v>39</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.2">
@@ -11652,7 +11652,7 @@
         <v>5</v>
       </c>
       <c r="G463">
-        <v>38.700000000000003</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.2">
@@ -11675,7 +11675,7 @@
         <v>5</v>
       </c>
       <c r="G464">
-        <v>38.4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.2">
@@ -11721,7 +11721,7 @@
         <v>5</v>
       </c>
       <c r="G466">
-        <v>38</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.2">
@@ -11744,7 +11744,7 @@
         <v>5</v>
       </c>
       <c r="G467">
-        <v>37.4</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.2">
@@ -11767,7 +11767,7 @@
         <v>5</v>
       </c>
       <c r="G468">
-        <v>37.299999999999997</v>
+        <v>39</v>
       </c>
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.2">
@@ -11790,7 +11790,7 @@
         <v>5</v>
       </c>
       <c r="G469">
-        <v>37.1</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.2">
@@ -11813,7 +11813,7 @@
         <v>5</v>
       </c>
       <c r="G470">
-        <v>43.5</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.2">
@@ -11836,7 +11836,7 @@
         <v>5</v>
       </c>
       <c r="G471">
-        <v>40.299999999999997</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.2">
@@ -11859,7 +11859,7 @@
         <v>5</v>
       </c>
       <c r="G472">
-        <v>40.299999999999997</v>
+        <v>39.799999999999997</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.2">
@@ -11882,7 +11882,7 @@
         <v>5</v>
       </c>
       <c r="G473">
-        <v>40.1</v>
+        <v>39.799999999999997</v>
       </c>
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.2">
@@ -11928,7 +11928,7 @@
         <v>5</v>
       </c>
       <c r="G475">
-        <v>39.799999999999997</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.2">
@@ -11951,7 +11951,7 @@
         <v>5</v>
       </c>
       <c r="G476">
-        <v>39.799999999999997</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.2">
@@ -11974,7 +11974,7 @@
         <v>5</v>
       </c>
       <c r="G477">
-        <v>39.6</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.2">
@@ -11997,7 +11997,7 @@
         <v>5</v>
       </c>
       <c r="G478">
-        <v>37.4</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.2">
@@ -12020,7 +12020,7 @@
         <v>5</v>
       </c>
       <c r="G479">
-        <v>43.2</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.2">
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G480">
-        <v>42.9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.2">
@@ -12066,7 +12066,7 @@
         <v>5</v>
       </c>
       <c r="G481">
-        <v>41.6</v>
+        <v>37.200000000000003</v>
       </c>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.2">
@@ -12089,7 +12089,7 @@
         <v>5</v>
       </c>
       <c r="G482">
-        <v>40.4</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.2">
@@ -12135,7 +12135,7 @@
         <v>5</v>
       </c>
       <c r="G484">
-        <v>39.4</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.2">
@@ -12158,7 +12158,7 @@
         <v>5</v>
       </c>
       <c r="G485">
-        <v>37.200000000000003</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.2">
@@ -12181,7 +12181,7 @@
         <v>5</v>
       </c>
       <c r="G486">
-        <v>37</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.2">
@@ -12204,7 +12204,7 @@
         <v>5</v>
       </c>
       <c r="G487">
-        <v>35.6</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.2">
@@ -12227,7 +12227,7 @@
         <v>5</v>
       </c>
       <c r="G488" s="6">
-        <v>41.4</v>
+        <v>37.799999999999997</v>
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.2">
@@ -12250,7 +12250,7 @@
         <v>5</v>
       </c>
       <c r="G489" s="6">
-        <v>40.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.2">
@@ -12273,7 +12273,7 @@
         <v>5</v>
       </c>
       <c r="G490" s="6">
-        <v>39.9</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.2">
@@ -12296,7 +12296,7 @@
         <v>5</v>
       </c>
       <c r="G491" s="6">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.2">
@@ -12342,7 +12342,7 @@
         <v>5</v>
       </c>
       <c r="G493" s="6">
-        <v>38.5</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.2">
@@ -12365,7 +12365,7 @@
         <v>5</v>
       </c>
       <c r="G494" s="6">
-        <v>38.1</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.2">
@@ -12388,7 +12388,7 @@
         <v>5</v>
       </c>
       <c r="G495" s="6">
-        <v>38.1</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.2">
@@ -12411,15 +12411,14 @@
         <v>5</v>
       </c>
       <c r="G496" s="6">
-        <v>37.799999999999997</v>
+        <v>41.4</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G233">
-    <sortCondition ref="E2:E233"/>
-    <sortCondition ref="C2:C233"/>
-    <sortCondition ref="D2:D233"/>
-    <sortCondition ref="A2:A233"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H497">
+    <sortCondition ref="B2:B497"/>
+    <sortCondition ref="A2:A497"/>
+    <sortCondition ref="G2:G497"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -12498,21 +12497,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008F3A2D606D2A7F41B72D5682D1CD7008" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d76c20a2b3afad6e4ced79b91df906ab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48b2884d-86bd-41bc-b5ea-f3a63e495149" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7e8f2e6da924d638fc8dc52abe2ab2bf" ns2:_="">
     <xsd:import namespace="48b2884d-86bd-41bc-b5ea-f3a63e495149"/>
@@ -12644,24 +12628,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7DAC2BA-C817-4ECF-8DFA-94F5C2AE87D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12677,4 +12659,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/leaf_temperatures.xlsx
+++ b/data/leaf_temperatures.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7F5A7E-B768-2D4D-BBBF-DDCCC4FA5B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB5337-6A00-AC44-980D-557A21B7533D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38100" yWindow="260" windowWidth="36160" windowHeight="20460" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15740" activeTab="1" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
   </bookViews>
   <sheets>
     <sheet name="temperatures" sheetId="5" r:id="rId1"/>
-    <sheet name="Read Me" sheetId="6" r:id="rId2"/>
+    <sheet name="highest_temps" sheetId="7" r:id="rId2"/>
+    <sheet name="Read Me" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">temperatures!$A$1:$H$497</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="28">
   <si>
     <t>Liriodendron tulipifera</t>
   </si>
@@ -12429,6 +12430,151 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DB13DA-F838-5846-BECE-6E196FC6D268}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1">
+        <v>2022</v>
+      </c>
+      <c r="C1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C2" s="2">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>38.9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45.3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>37.6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2">
+        <v>40.6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>40.700000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="C9" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45.7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2">
+        <v>41.9</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45.9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>42.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD35868-CDA1-6442-B101-D76AB4DBCDD5}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -12629,18 +12775,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12662,18 +12808,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/leaf_temperatures.xlsx
+++ b/data/leaf_temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB5337-6A00-AC44-980D-557A21B7533D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD061F2-4505-1B40-8BA2-91B6595E7285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15740" activeTab="1" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="29">
   <si>
     <t>Liriodendron tulipifera</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Celtis laevigata</t>
-  </si>
-  <si>
-    <t>Ulmus americana</t>
   </si>
   <si>
     <t>Juglans nigra</t>
@@ -124,6 +121,12 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>Ulmus rubra</t>
+  </si>
+  <si>
+    <t>leaf_temp</t>
   </si>
 </sst>
 </file>
@@ -520,28 +523,28 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I1" s="2"/>
     </row>
@@ -1018,7 +1021,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" s="7">
         <v>44747</v>
@@ -1043,7 +1046,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="7">
         <v>44747</v>
@@ -1068,7 +1071,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="7">
         <v>44747</v>
@@ -1093,7 +1096,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="7">
         <v>44747</v>
@@ -1118,7 +1121,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" s="7">
         <v>44747</v>
@@ -1143,7 +1146,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B25" s="7">
         <v>44747</v>
@@ -1168,7 +1171,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26" s="7">
         <v>44747</v>
@@ -1193,7 +1196,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" s="7">
         <v>44747</v>
@@ -1218,7 +1221,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="7">
         <v>44747</v>
@@ -1243,7 +1246,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="7">
         <v>44747</v>
@@ -1268,7 +1271,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B30" s="7">
         <v>44747</v>
@@ -1293,7 +1296,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B31" s="7">
         <v>44747</v>
@@ -1318,7 +1321,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" s="7">
         <v>44747</v>
@@ -1343,7 +1346,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33" s="7">
         <v>44747</v>
@@ -1368,7 +1371,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B34" s="7">
         <v>44747</v>
@@ -1393,7 +1396,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" s="7">
         <v>44747</v>
@@ -1418,7 +1421,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B36" s="7">
         <v>44747</v>
@@ -1443,7 +1446,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B37" s="7">
         <v>44747</v>
@@ -1918,7 +1921,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B56" s="7">
         <v>44747</v>
@@ -1943,7 +1946,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B57" s="7">
         <v>44747</v>
@@ -1968,7 +1971,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B58" s="7">
         <v>44747</v>
@@ -1993,7 +1996,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B59" s="7">
         <v>44747</v>
@@ -2018,7 +2021,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" s="7">
         <v>44747</v>
@@ -2043,7 +2046,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B61" s="7">
         <v>44747</v>
@@ -2068,7 +2071,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B62" s="7">
         <v>44747</v>
@@ -2093,7 +2096,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B63" s="7">
         <v>44747</v>
@@ -2118,7 +2121,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B64" s="7">
         <v>44747</v>
@@ -2818,7 +2821,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B92" s="7">
         <v>44747</v>
@@ -2843,7 +2846,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B93" s="7">
         <v>44747</v>
@@ -2868,7 +2871,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B94" s="7">
         <v>44747</v>
@@ -2893,7 +2896,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B95" s="7">
         <v>44747</v>
@@ -2918,7 +2921,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B96" s="7">
         <v>44747</v>
@@ -2943,7 +2946,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B97" s="7">
         <v>44747</v>
@@ -2968,7 +2971,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B98" s="7">
         <v>44747</v>
@@ -2993,7 +2996,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B99" s="7">
         <v>44747</v>
@@ -3018,7 +3021,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B100" s="7">
         <v>44747</v>
@@ -3493,7 +3496,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B119" s="7">
         <v>44754</v>
@@ -3518,7 +3521,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B120" s="7">
         <v>44754</v>
@@ -3543,7 +3546,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121" s="7">
         <v>44754</v>
@@ -3568,7 +3571,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B122" s="7">
         <v>44754</v>
@@ -3593,7 +3596,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B123" s="7">
         <v>44754</v>
@@ -3618,7 +3621,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B124" s="7">
         <v>44754</v>
@@ -3643,7 +3646,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B125" s="7">
         <v>44754</v>
@@ -3668,7 +3671,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B126" s="7">
         <v>44754</v>
@@ -3693,7 +3696,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B127" s="7">
         <v>44754</v>
@@ -3718,7 +3721,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B128" s="7">
         <v>44754</v>
@@ -3743,7 +3746,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B129" s="7">
         <v>44754</v>
@@ -3768,7 +3771,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B130" s="7">
         <v>44754</v>
@@ -3793,7 +3796,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B131" s="7">
         <v>44754</v>
@@ -3818,7 +3821,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B132" s="7">
         <v>44754</v>
@@ -3843,7 +3846,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B133" s="7">
         <v>44754</v>
@@ -3868,7 +3871,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B134" s="7">
         <v>44754</v>
@@ -3893,7 +3896,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B135" s="7">
         <v>44754</v>
@@ -3918,7 +3921,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B136" s="7">
         <v>44754</v>
@@ -4393,7 +4396,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B155" s="7">
         <v>44754</v>
@@ -4418,7 +4421,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B156" s="7">
         <v>44754</v>
@@ -4443,7 +4446,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B157" s="7">
         <v>44754</v>
@@ -4468,7 +4471,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B158" s="7">
         <v>44754</v>
@@ -4493,7 +4496,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B159" s="7">
         <v>44754</v>
@@ -4518,7 +4521,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B160" s="7">
         <v>44754</v>
@@ -4543,7 +4546,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B161" s="7">
         <v>44754</v>
@@ -4568,7 +4571,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B162" s="7">
         <v>44754</v>
@@ -4593,7 +4596,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B163" s="7">
         <v>44754</v>
@@ -5293,7 +5296,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B191" s="7">
         <v>44754</v>
@@ -5318,7 +5321,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B192" s="7">
         <v>44754</v>
@@ -5343,7 +5346,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B193" s="7">
         <v>44754</v>
@@ -5368,7 +5371,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B194" s="7">
         <v>44754</v>
@@ -5393,7 +5396,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B195" s="7">
         <v>44754</v>
@@ -5418,7 +5421,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B196" s="7">
         <v>44754</v>
@@ -5443,7 +5446,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B197" s="7">
         <v>44754</v>
@@ -5468,7 +5471,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B198" s="7">
         <v>44754</v>
@@ -5493,7 +5496,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B199" s="7">
         <v>44754</v>
@@ -5968,7 +5971,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B218" s="7">
         <v>44756</v>
@@ -5993,7 +5996,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B219" s="7">
         <v>44756</v>
@@ -6018,7 +6021,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B220" s="7">
         <v>44756</v>
@@ -6043,7 +6046,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B221" s="7">
         <v>44756</v>
@@ -6068,7 +6071,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B222" s="7">
         <v>44756</v>
@@ -6093,7 +6096,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B223" s="7">
         <v>44756</v>
@@ -6118,7 +6121,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B224" s="7">
         <v>44756</v>
@@ -6143,7 +6146,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B225" s="7">
         <v>44756</v>
@@ -6168,7 +6171,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B226" s="7">
         <v>44756</v>
@@ -6193,7 +6196,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B227" s="7">
         <v>44756</v>
@@ -6217,7 +6220,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B228" s="7">
         <v>44756</v>
@@ -6241,7 +6244,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B229" s="7">
         <v>44756</v>
@@ -6266,7 +6269,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B230" s="7">
         <v>44756</v>
@@ -6291,7 +6294,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B231" s="7">
         <v>44756</v>
@@ -6316,7 +6319,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B232" s="7">
         <v>44756</v>
@@ -6341,7 +6344,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B233" s="7">
         <v>44756</v>
@@ -6366,7 +6369,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B234" s="7">
         <v>44756</v>
@@ -6390,7 +6393,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B235" s="7">
         <v>44756</v>
@@ -6828,7 +6831,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B254" s="7">
         <v>44756</v>
@@ -6851,7 +6854,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B255" s="7">
         <v>44756</v>
@@ -6874,7 +6877,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B256" s="7">
         <v>44756</v>
@@ -6897,7 +6900,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B257" s="7">
         <v>44756</v>
@@ -6920,7 +6923,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B258" s="7">
         <v>44756</v>
@@ -6943,7 +6946,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B259" s="7">
         <v>44756</v>
@@ -6966,7 +6969,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B260" s="7">
         <v>44756</v>
@@ -6989,7 +6992,7 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B261" s="7">
         <v>44756</v>
@@ -7012,7 +7015,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B262" s="7">
         <v>44756</v>
@@ -7656,7 +7659,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B290" s="7">
         <v>44756</v>
@@ -7679,7 +7682,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B291" s="7">
         <v>44756</v>
@@ -7702,7 +7705,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B292" s="7">
         <v>44756</v>
@@ -7725,7 +7728,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B293" s="7">
         <v>44756</v>
@@ -7748,7 +7751,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B294" s="7">
         <v>44756</v>
@@ -7771,7 +7774,7 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B295" s="7">
         <v>44756</v>
@@ -7794,7 +7797,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B296" s="7">
         <v>44756</v>
@@ -7817,7 +7820,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B297" s="7">
         <v>44756</v>
@@ -7840,7 +7843,7 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B298" s="7">
         <v>44756</v>
@@ -8277,7 +8280,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B317" s="7">
         <v>45161</v>
@@ -8295,12 +8298,12 @@
         <v>4</v>
       </c>
       <c r="H317" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B318" s="7">
         <v>45161</v>
@@ -8318,12 +8321,12 @@
         <v>4</v>
       </c>
       <c r="H318" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B319" s="7">
         <v>45161</v>
@@ -8341,12 +8344,12 @@
         <v>4</v>
       </c>
       <c r="H319" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B320" s="7">
         <v>45161</v>
@@ -8364,12 +8367,12 @@
         <v>4</v>
       </c>
       <c r="H320" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B321" s="7">
         <v>45161</v>
@@ -8387,12 +8390,12 @@
         <v>4</v>
       </c>
       <c r="H321" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B322" s="7">
         <v>45161</v>
@@ -8410,12 +8413,12 @@
         <v>4</v>
       </c>
       <c r="H322" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B323" s="7">
         <v>45161</v>
@@ -8433,12 +8436,12 @@
         <v>4</v>
       </c>
       <c r="H323" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B324" s="7">
         <v>45161</v>
@@ -8456,12 +8459,12 @@
         <v>4</v>
       </c>
       <c r="H324" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B325" s="7">
         <v>45161</v>
@@ -8479,12 +8482,12 @@
         <v>4</v>
       </c>
       <c r="H325" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B326" s="7">
         <v>45161</v>
@@ -8507,7 +8510,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B327" s="7">
         <v>45161</v>
@@ -8530,7 +8533,7 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B328" s="7">
         <v>45161</v>
@@ -8553,7 +8556,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B329" s="7">
         <v>45161</v>
@@ -8576,7 +8579,7 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B330" s="7">
         <v>45161</v>
@@ -8599,7 +8602,7 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B331" s="7">
         <v>45161</v>
@@ -8622,7 +8625,7 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B332" s="7">
         <v>45161</v>
@@ -8645,7 +8648,7 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B333" s="7">
         <v>45161</v>
@@ -8668,7 +8671,7 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B334" s="7">
         <v>45161</v>
@@ -9105,7 +9108,7 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B353" s="7">
         <v>45161</v>
@@ -9128,7 +9131,7 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B354" s="7">
         <v>45161</v>
@@ -9151,7 +9154,7 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B355" s="7">
         <v>45161</v>
@@ -9174,7 +9177,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B356" s="7">
         <v>45161</v>
@@ -9197,7 +9200,7 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B357" s="7">
         <v>45161</v>
@@ -9220,7 +9223,7 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B358" s="7">
         <v>45161</v>
@@ -9243,7 +9246,7 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B359" s="7">
         <v>45161</v>
@@ -9266,7 +9269,7 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B360" s="7">
         <v>45161</v>
@@ -9289,7 +9292,7 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B361" s="7">
         <v>45161</v>
@@ -9933,7 +9936,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B389" s="7">
         <v>45161</v>
@@ -9956,7 +9959,7 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B390" s="7">
         <v>45161</v>
@@ -9979,7 +9982,7 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B391" s="7">
         <v>45161</v>
@@ -10002,7 +10005,7 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B392" s="7">
         <v>45161</v>
@@ -10025,7 +10028,7 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B393" s="7">
         <v>45161</v>
@@ -10048,7 +10051,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B394" s="7">
         <v>45161</v>
@@ -10071,7 +10074,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B395" s="7">
         <v>45161</v>
@@ -10094,7 +10097,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B396" s="7">
         <v>45161</v>
@@ -10117,7 +10120,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B397" s="7">
         <v>45161</v>
@@ -10554,7 +10557,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B416" s="7">
         <v>45163</v>
@@ -10577,7 +10580,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B417" s="7">
         <v>45163</v>
@@ -10600,7 +10603,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B418" s="7">
         <v>45163</v>
@@ -10623,7 +10626,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B419" s="7">
         <v>45163</v>
@@ -10646,7 +10649,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B420" s="7">
         <v>45163</v>
@@ -10669,7 +10672,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B421" s="7">
         <v>45163</v>
@@ -10692,7 +10695,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B422" s="7">
         <v>45163</v>
@@ -10715,7 +10718,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B423" s="7">
         <v>45163</v>
@@ -10738,7 +10741,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B424" s="7">
         <v>45163</v>
@@ -10761,7 +10764,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B425" s="7">
         <v>45163</v>
@@ -10784,7 +10787,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B426" s="7">
         <v>45163</v>
@@ -10807,7 +10810,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B427" s="7">
         <v>45163</v>
@@ -10830,7 +10833,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B428" s="7">
         <v>45163</v>
@@ -10853,7 +10856,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B429" s="7">
         <v>45163</v>
@@ -10876,7 +10879,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B430" s="7">
         <v>45163</v>
@@ -10899,7 +10902,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B431" s="7">
         <v>45163</v>
@@ -10922,7 +10925,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B432" s="7">
         <v>45163</v>
@@ -10945,7 +10948,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B433" s="7">
         <v>45163</v>
@@ -11382,7 +11385,7 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B452" s="7">
         <v>45163</v>
@@ -11405,7 +11408,7 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B453" s="7">
         <v>45163</v>
@@ -11428,7 +11431,7 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B454" s="7">
         <v>45163</v>
@@ -11451,7 +11454,7 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B455" s="7">
         <v>45163</v>
@@ -11474,7 +11477,7 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B456" s="7">
         <v>45163</v>
@@ -11497,7 +11500,7 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B457" s="7">
         <v>45163</v>
@@ -11520,7 +11523,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B458" s="7">
         <v>45163</v>
@@ -11543,7 +11546,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B459" s="7">
         <v>45163</v>
@@ -11566,7 +11569,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B460" s="7">
         <v>45163</v>
@@ -12210,7 +12213,7 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A488" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B488" s="7">
         <v>45163</v>
@@ -12233,7 +12236,7 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A489" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B489" s="7">
         <v>45163</v>
@@ -12256,7 +12259,7 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A490" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B490" s="7">
         <v>45163</v>
@@ -12279,7 +12282,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A491" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B491" s="7">
         <v>45163</v>
@@ -12302,7 +12305,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A492" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B492" s="7">
         <v>45163</v>
@@ -12325,7 +12328,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A493" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B493" s="7">
         <v>45163</v>
@@ -12348,7 +12351,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A494" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B494" s="7">
         <v>45163</v>
@@ -12371,7 +12374,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A495" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B495" s="7">
         <v>45163</v>
@@ -12394,7 +12397,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A496" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B496" s="7">
         <v>45163</v>
@@ -12431,141 +12434,263 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DB13DA-F838-5846-BECE-6E196FC6D268}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1">
-        <v>2022</v>
-      </c>
-      <c r="C1">
-        <v>2023</v>
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
+        <v>2022</v>
+      </c>
+      <c r="C2" s="2">
         <v>38.799999999999997</v>
-      </c>
-      <c r="C2" s="2">
-        <v>43.5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
+        <v>2022</v>
+      </c>
+      <c r="C3" s="2">
         <v>38.9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2022</v>
+      </c>
+      <c r="C4" s="2">
         <v>45.3</v>
-      </c>
-      <c r="C4" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>2022</v>
+      </c>
+      <c r="C5" s="2">
         <v>37.6</v>
-      </c>
-      <c r="C5" s="2">
-        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
+        <v>2022</v>
+      </c>
+      <c r="C6" s="2">
         <v>36.5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
+        <v>2022</v>
+      </c>
+      <c r="C7" s="2">
         <v>44.5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>44.8</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>2022</v>
+      </c>
+      <c r="C8" s="2">
         <v>40.6</v>
-      </c>
-      <c r="C8" s="2">
-        <v>40.700000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
+        <v>2022</v>
+      </c>
+      <c r="C9" s="2">
         <v>40.200000000000003</v>
-      </c>
-      <c r="C9" s="2">
-        <v>39.5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
+        <v>2022</v>
+      </c>
+      <c r="C10" s="2">
         <v>45.7</v>
-      </c>
-      <c r="C10" s="2">
-        <v>43.5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
+        <v>2022</v>
+      </c>
+      <c r="C11" s="2">
         <v>41.9</v>
-      </c>
-      <c r="C11" s="2">
-        <v>45.3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>2022</v>
+      </c>
+      <c r="C12" s="2">
         <v>45.9</v>
       </c>
-      <c r="C12" s="2">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="2">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>2023</v>
+      </c>
+      <c r="C14" s="2">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <v>2023</v>
+      </c>
+      <c r="C15" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>2023</v>
+      </c>
+      <c r="C16" s="2">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>2023</v>
+      </c>
+      <c r="C17" s="2">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>2023</v>
+      </c>
+      <c r="C18" s="2">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2023</v>
+      </c>
+      <c r="C19" s="2">
+        <v>40.700000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>2023</v>
+      </c>
+      <c r="C21" s="2">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>2023</v>
+      </c>
+      <c r="C22" s="2">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
+        <v>2023</v>
+      </c>
+      <c r="C23" s="2">
         <v>42.1</v>
       </c>
     </row>
@@ -12584,17 +12709,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -12602,7 +12727,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -12610,7 +12735,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -12618,7 +12743,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -12626,7 +12751,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -12634,7 +12759,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -12643,6 +12768,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008F3A2D606D2A7F41B72D5682D1CD7008" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d76c20a2b3afad6e4ced79b91df906ab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48b2884d-86bd-41bc-b5ea-f3a63e495149" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7e8f2e6da924d638fc8dc52abe2ab2bf" ns2:_="">
     <xsd:import namespace="48b2884d-86bd-41bc-b5ea-f3a63e495149"/>
@@ -12774,22 +12914,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7DAC2BA-C817-4ECF-8DFA-94F5C2AE87D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12805,21 +12947,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/leaf_temperatures.xlsx
+++ b/data/leaf_temperatures.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD061F2-4505-1B40-8BA2-91B6595E7285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01248CE0-91B7-F34F-913F-95A24656A7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15740" activeTab="1" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
+    <workbookView xWindow="-37640" yWindow="1420" windowWidth="28800" windowHeight="15740" activeTab="1" xr2:uid="{0D1DAA0C-3E7A-A94D-99AC-B432AD39DBD7}"/>
   </bookViews>
   <sheets>
     <sheet name="temperatures" sheetId="5" r:id="rId1"/>
@@ -12768,21 +12768,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008F3A2D606D2A7F41B72D5682D1CD7008" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d76c20a2b3afad6e4ced79b91df906ab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48b2884d-86bd-41bc-b5ea-f3a63e495149" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7e8f2e6da924d638fc8dc52abe2ab2bf" ns2:_="">
     <xsd:import namespace="48b2884d-86bd-41bc-b5ea-f3a63e495149"/>
@@ -12914,24 +12899,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7DAC2BA-C817-4ECF-8DFA-94F5C2AE87D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12947,4 +12930,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFB0FA-CD1A-4F5C-B895-89C67E76B7DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CB64D7-F540-4BAF-99C7-751D0C161C11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>